--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/2882-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/2882-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7B1F16DF-85A3-4913-B4D2-00C92C1C95CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BF40AB9B-A4AA-4BF5-AB85-667D239C2791}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{557B778D-BD8A-4691-9AF0-69549CA9B75E}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{BEF6924B-D50D-42BF-B159-CC8F31065471}"/>
   </bookViews>
   <sheets>
     <sheet name="2882-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1565,29 +1565,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70BD9169-65A0-48F0-9C41-657A9405EF3D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AF56BD1-01FE-4A7F-AFA9-D52698D1A8AD}">
   <dimension ref="A1:X35"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="4" width="6.25" customWidth="1"/>
-    <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="7" width="6.25" customWidth="1"/>
-    <col min="8" max="8" width="6" customWidth="1"/>
-    <col min="9" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="15" width="6.25" customWidth="1"/>
-    <col min="16" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="6.25" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1621,7 +1620,7 @@
       <c r="W1" s="30"/>
       <c r="X1" s="22"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1657,7 +1656,7 @@
       <c r="W2" s="32"/>
       <c r="X2" s="33"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1709,7 +1708,7 @@
       </c>
       <c r="X3" s="36"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1777,7 +1776,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="37">
         <v>2024</v>
       </c>
@@ -1849,7 +1848,7 @@
         <v>7.07</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="39">
         <v>2023</v>
       </c>
@@ -1921,7 +1920,7 @@
         <v>4.6399999999999997</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="37">
         <v>2022</v>
       </c>
@@ -1993,7 +1992,7 @@
         <v>2.2599999999999998</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="39">
         <v>2021</v>
       </c>
@@ -2065,7 +2064,7 @@
         <v>9.66</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="37">
         <v>2020</v>
       </c>
@@ -2137,7 +2136,7 @@
         <v>6.27</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="39">
         <v>2019</v>
       </c>
@@ -2209,7 +2208,7 @@
         <v>5.92</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="37">
         <v>2018</v>
       </c>
@@ -2281,7 +2280,7 @@
         <v>3.86</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="39">
         <v>2017</v>
       </c>
@@ -2353,7 +2352,7 @@
         <v>5.45</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="37">
         <v>2016</v>
       </c>
@@ -2425,7 +2424,7 @@
         <v>4.34</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="39">
         <v>2015</v>
       </c>
@@ -2497,7 +2496,7 @@
         <v>5.95</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="37">
         <v>2014</v>
       </c>
@@ -2569,7 +2568,7 @@
         <v>5.18</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="41">
         <v>2013</v>
       </c>
@@ -2641,7 +2640,7 @@
         <v>4.75</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="43"/>
       <c r="B17" s="44"/>
       <c r="C17" s="18" t="s">
@@ -2669,7 +2668,7 @@
       <c r="W17" s="50"/>
       <c r="X17" s="46"/>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="37">
         <v>2012</v>
       </c>
@@ -2741,7 +2740,7 @@
         <v>4.42</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="41">
         <v>2011</v>
       </c>
@@ -2813,7 +2812,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="43"/>
       <c r="B20" s="44"/>
       <c r="C20" s="18" t="s">
@@ -2841,7 +2840,7 @@
       <c r="W20" s="50"/>
       <c r="X20" s="46"/>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="51">
         <v>2010</v>
       </c>
@@ -2913,7 +2912,7 @@
         <v>2.86</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="53"/>
       <c r="B22" s="54"/>
       <c r="C22" s="20" t="s">
@@ -2941,7 +2940,7 @@
       <c r="W22" s="60"/>
       <c r="X22" s="56"/>
     </row>
-    <row r="23" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="41">
         <v>2009</v>
       </c>
@@ -3013,7 +3012,7 @@
         <v>2.34</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="43"/>
       <c r="B24" s="44"/>
       <c r="C24" s="18" t="s">
@@ -3041,7 +3040,7 @@
       <c r="W24" s="50"/>
       <c r="X24" s="46"/>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="37">
         <v>2008</v>
       </c>
@@ -3113,7 +3112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="41">
         <v>2007</v>
       </c>
@@ -3185,7 +3184,7 @@
         <v>10.7</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="43"/>
       <c r="B27" s="44"/>
       <c r="C27" s="18" t="s">
@@ -3213,7 +3212,7 @@
       <c r="W27" s="50"/>
       <c r="X27" s="46"/>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="37">
         <v>2006</v>
       </c>
@@ -3285,7 +3284,7 @@
         <v>2.36</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="41">
         <v>2005</v>
       </c>
@@ -3357,7 +3356,7 @@
         <v>3.49</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="43"/>
       <c r="B30" s="44"/>
       <c r="C30" s="18" t="s">
@@ -3385,7 +3384,7 @@
       <c r="W30" s="50"/>
       <c r="X30" s="46"/>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="37">
         <v>2004</v>
       </c>
@@ -3457,7 +3456,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="39">
         <v>2003</v>
       </c>
@@ -3529,7 +3528,7 @@
         <v>3.92</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="37">
         <v>2002</v>
       </c>
@@ -3601,7 +3600,7 @@
         <v>4.13</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="39">
         <v>2001</v>
       </c>
@@ -3673,7 +3672,7 @@
         <v>4.3499999999999996</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="37" t="s">
         <v>57</v>
       </c>
